--- a/public/sampleExcel/products_sample.xlsx
+++ b/public/sampleExcel/products_sample.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vun.Thy\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\prodsystem\public\sampleExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964ADF95-660F-446A-9A60-7A40BCF1FC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA115E98-F998-4BE1-A056-653018CAE58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>item_code</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>variant_attributes</t>
+  </si>
+  <si>
+    <t>key_words</t>
   </si>
 </sst>
 </file>
@@ -404,78 +407,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
     </row>
